--- a/Claude outputs/Mare_Durabilis_Planning_financier_2026_2029_FDD.xlsx
+++ b/Claude outputs/Mare_Durabilis_Planning_financier_2026_2029_FDD.xlsx
@@ -819,199 +819,199 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1847,39 +1847,39 @@
       </c>
       <c r="J19" s="15" t="n">
         <f aca="false">'Circuit public'!D21/4</f>
-        <v>5136.629575</v>
+        <v>5526.194575</v>
       </c>
       <c r="K19" s="15" t="n">
         <f aca="false">'Circuit public'!D21/4</f>
-        <v>5136.629575</v>
+        <v>5526.194575</v>
       </c>
       <c r="L19" s="15" t="n">
         <f aca="false">'Circuit public'!D21/4</f>
-        <v>5136.629575</v>
+        <v>5526.194575</v>
       </c>
       <c r="M19" s="15" t="n">
         <f aca="false">'Circuit public'!D21/4</f>
-        <v>5136.629575</v>
+        <v>5526.194575</v>
       </c>
       <c r="N19" s="15" t="n">
         <f aca="false">'Circuit public'!E21/4</f>
-        <v>5250.6823</v>
+        <v>8016.7423</v>
       </c>
       <c r="O19" s="15" t="n">
         <f aca="false">'Circuit public'!E21/4</f>
-        <v>5250.6823</v>
+        <v>8016.7423</v>
       </c>
       <c r="P19" s="15" t="n">
         <f aca="false">'Circuit public'!E21/4</f>
-        <v>5250.6823</v>
+        <v>8016.7423</v>
       </c>
       <c r="Q19" s="15" t="n">
         <f aca="false">'Circuit public'!E21/4</f>
-        <v>5250.6823</v>
+        <v>8016.7423</v>
       </c>
       <c r="R19" s="15" t="n">
         <f aca="false">SUM(B19:Q19)</f>
-        <v>56873.9983</v>
+        <v>69496.4983</v>
       </c>
       <c r="S19" s="15"/>
       <c r="T19" s="15"/>
@@ -1925,39 +1925,39 @@
       </c>
       <c r="J20" s="21" t="n">
         <f aca="false">SUM(J17:J19)</f>
-        <v>5136.629575</v>
+        <v>5526.194575</v>
       </c>
       <c r="K20" s="21" t="n">
         <f aca="false">SUM(K17:K19)</f>
-        <v>5136.629575</v>
+        <v>5526.194575</v>
       </c>
       <c r="L20" s="21" t="n">
         <f aca="false">SUM(L17:L19)</f>
-        <v>5136.629575</v>
+        <v>5526.194575</v>
       </c>
       <c r="M20" s="21" t="n">
         <f aca="false">SUM(M17:M19)</f>
-        <v>11772.429575</v>
+        <v>12161.994575</v>
       </c>
       <c r="N20" s="21" t="n">
         <f aca="false">SUM(N17:N19)</f>
-        <v>5250.6823</v>
+        <v>8016.7423</v>
       </c>
       <c r="O20" s="21" t="n">
         <f aca="false">SUM(O17:O19)</f>
-        <v>5250.6823</v>
+        <v>8016.7423</v>
       </c>
       <c r="P20" s="21" t="n">
         <f aca="false">SUM(P17:P19)</f>
-        <v>5250.6823</v>
+        <v>8016.7423</v>
       </c>
       <c r="Q20" s="21" t="n">
         <f aca="false">SUM(Q17:Q19)</f>
-        <v>12132.7723</v>
+        <v>14898.8323</v>
       </c>
       <c r="R20" s="15" t="n">
         <f aca="false">SUM(B20:Q20)</f>
-        <v>73430.4883</v>
+        <v>86052.9883</v>
       </c>
       <c r="S20" s="15"/>
       <c r="T20" s="15"/>
@@ -2658,39 +2658,39 @@
       </c>
       <c r="J34" s="23" t="n">
         <f aca="false">J13+J20+J32</f>
-        <v>76795.329575</v>
+        <v>77184.894575</v>
       </c>
       <c r="K34" s="23" t="n">
         <f aca="false">K13+K20+K32</f>
-        <v>171445.329575</v>
+        <v>171834.894575</v>
       </c>
       <c r="L34" s="23" t="n">
         <f aca="false">L13+L20+L32</f>
-        <v>2013445.329575</v>
+        <v>2013834.894575</v>
       </c>
       <c r="M34" s="23" t="n">
         <f aca="false">M13+M20+M32</f>
-        <v>67081.129575</v>
+        <v>67470.694575</v>
       </c>
       <c r="N34" s="23" t="n">
         <f aca="false">N13+N20+N32</f>
-        <v>96474.4543</v>
+        <v>99240.5143</v>
       </c>
       <c r="O34" s="23" t="n">
         <f aca="false">O13+O20+O32</f>
-        <v>171624.4543</v>
+        <v>174390.5143</v>
       </c>
       <c r="P34" s="23" t="n">
         <f aca="false">P13+P20+P32</f>
-        <v>13624.4543</v>
+        <v>16390.5143</v>
       </c>
       <c r="Q34" s="23" t="n">
         <f aca="false">Q13+Q20+Q32</f>
-        <v>69506.5443</v>
+        <v>72272.6043</v>
       </c>
       <c r="R34" s="23" t="n">
         <f aca="false">SUM(B34:Q34)</f>
-        <v>3946065.9763</v>
+        <v>3958688.4763</v>
       </c>
       <c r="S34" s="8"/>
       <c r="T34" s="8"/>
@@ -2734,35 +2734,35 @@
       </c>
       <c r="J35" s="15" t="n">
         <f aca="false">I35+J34</f>
-        <v>1342864.280375</v>
+        <v>1343253.845375</v>
       </c>
       <c r="K35" s="15" t="n">
         <f aca="false">J35+K34</f>
-        <v>1514309.60995</v>
+        <v>1515088.73995</v>
       </c>
       <c r="L35" s="15" t="n">
         <f aca="false">K35+L34</f>
-        <v>3527754.939525</v>
+        <v>3528923.634525</v>
       </c>
       <c r="M35" s="15" t="n">
         <f aca="false">L35+M34</f>
-        <v>3594836.0691</v>
+        <v>3596394.3291</v>
       </c>
       <c r="N35" s="15" t="n">
         <f aca="false">M35+N34</f>
-        <v>3691310.5234</v>
+        <v>3695634.8434</v>
       </c>
       <c r="O35" s="15" t="n">
         <f aca="false">N35+O34</f>
-        <v>3862934.9777</v>
+        <v>3870025.3577</v>
       </c>
       <c r="P35" s="15" t="n">
         <f aca="false">O35+P34</f>
-        <v>3876559.432</v>
+        <v>3886415.872</v>
       </c>
       <c r="Q35" s="15" t="n">
         <f aca="false">P35+Q34</f>
-        <v>3946065.9763</v>
+        <v>3958688.4763</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3040,7 +3040,7 @@
       <c r="E44" s="29"/>
       <c r="F44" s="28" t="n">
         <f aca="false">MAX(0,K35-SUM(B40:K40)-R43)+SUM(L20:Q20)+SUM(L32:Q32)+M9+Q9</f>
-        <v>1562447.0255</v>
+        <v>1575069.5255</v>
       </c>
       <c r="G44" s="27"/>
       <c r="H44" s="27"/>
@@ -3055,7 +3055,7 @@
       <c r="Q44" s="27"/>
       <c r="R44" s="12" t="n">
         <f aca="false">SUM(B44:Q44)</f>
-        <v>1562447.0255</v>
+        <v>1575069.5255</v>
       </c>
       <c r="U44" s="13" t="s">
         <v>83</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F49" s="23" t="n">
         <f aca="false">SUM(F43:F48)</f>
-        <v>1562522.0255</v>
+        <v>1575144.5255</v>
       </c>
       <c r="G49" s="23" t="n">
         <f aca="false">SUM(G43:G48)</f>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="R49" s="23" t="n">
         <f aca="false">SUM(B49:Q49)</f>
-        <v>3946065.9763</v>
+        <v>3958688.4763</v>
       </c>
       <c r="S49" s="8"/>
       <c r="T49" s="8"/>
@@ -3386,51 +3386,51 @@
       </c>
       <c r="F50" s="15" t="n">
         <f aca="false">E50+F49</f>
-        <v>1727315.9763</v>
+        <v>1739938.4763</v>
       </c>
       <c r="G50" s="15" t="n">
         <f aca="false">F50+G49</f>
-        <v>1727465.9763</v>
+        <v>1740088.4763</v>
       </c>
       <c r="H50" s="15" t="n">
         <f aca="false">G50+H49</f>
-        <v>1727615.9763</v>
+        <v>1740238.4763</v>
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">H50+I49</f>
-        <v>1727765.9763</v>
+        <v>1740388.4763</v>
       </c>
       <c r="J50" s="15" t="n">
         <f aca="false">I50+J49</f>
-        <v>1727990.9763</v>
+        <v>1740613.4763</v>
       </c>
       <c r="K50" s="15" t="n">
         <f aca="false">J50+K49</f>
-        <v>3944715.9763</v>
+        <v>3957338.4763</v>
       </c>
       <c r="L50" s="15" t="n">
         <f aca="false">K50+L49</f>
-        <v>3944940.9763</v>
+        <v>3957563.4763</v>
       </c>
       <c r="M50" s="15" t="n">
         <f aca="false">L50+M49</f>
-        <v>3945165.9763</v>
+        <v>3957788.4763</v>
       </c>
       <c r="N50" s="15" t="n">
         <f aca="false">M50+N49</f>
-        <v>3945390.9763</v>
+        <v>3958013.4763</v>
       </c>
       <c r="O50" s="15" t="n">
         <f aca="false">N50+O49</f>
-        <v>3945615.9763</v>
+        <v>3958238.4763</v>
       </c>
       <c r="P50" s="15" t="n">
         <f aca="false">O50+P49</f>
-        <v>3945840.9763</v>
+        <v>3958463.4763</v>
       </c>
       <c r="Q50" s="15" t="n">
         <f aca="false">P50+Q49</f>
-        <v>3946065.9763</v>
+        <v>3958688.4763</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3481,47 +3481,47 @@
       </c>
       <c r="F53" s="10" t="n">
         <f aca="false">F50-F35</f>
-        <v>1499279.8886</v>
+        <v>1511902.3886</v>
       </c>
       <c r="G53" s="10" t="n">
         <f aca="false">G50-G35</f>
-        <v>1337163.8009</v>
+        <v>1349786.3009</v>
       </c>
       <c r="H53" s="10" t="n">
         <f aca="false">H50-H35</f>
-        <v>517889.7132</v>
+        <v>530512.2132</v>
       </c>
       <c r="I53" s="10" t="n">
         <f aca="false">I50-I35</f>
-        <v>461697.0255</v>
+        <v>474319.5255</v>
       </c>
       <c r="J53" s="10" t="n">
         <f aca="false">J50-J35</f>
-        <v>385126.695925</v>
+        <v>397359.630925</v>
       </c>
       <c r="K53" s="10" t="n">
         <f aca="false">K50-K35</f>
-        <v>2430406.36635</v>
+        <v>2442249.73635</v>
       </c>
       <c r="L53" s="10" t="n">
         <f aca="false">L50-L35</f>
-        <v>417186.036774999</v>
+        <v>428639.841775</v>
       </c>
       <c r="M53" s="10" t="n">
         <f aca="false">M50-M35</f>
-        <v>350329.907199999</v>
+        <v>361394.1472</v>
       </c>
       <c r="N53" s="10" t="n">
         <f aca="false">N50-N35</f>
-        <v>254080.452899999</v>
+        <v>262378.6329</v>
       </c>
       <c r="O53" s="10" t="n">
         <f aca="false">O50-O35</f>
-        <v>82680.9985999996</v>
+        <v>88213.1186000002</v>
       </c>
       <c r="P53" s="10" t="n">
         <f aca="false">P50-P35</f>
-        <v>69281.5442999997</v>
+        <v>72047.6043000002</v>
       </c>
       <c r="Q53" s="10" t="n">
         <f aca="false">Q50-Q35</f>
@@ -3767,15 +3767,15 @@
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">SUM('Planning financier'!J20:M20)</f>
-        <v>27182.3183</v>
+        <v>28740.5783</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">SUM('Planning financier'!N20:Q20)</f>
-        <v>27884.8192</v>
+        <v>38949.0592</v>
       </c>
       <c r="F5" s="12" t="n">
         <f aca="false">SUM(B5:E5)</f>
-        <v>73430.4883</v>
+        <v>86052.9883</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3817,15 +3817,15 @@
       </c>
       <c r="D7" s="12" t="n">
         <f aca="false">SUM('Planning financier'!J34:M34)</f>
-        <v>2328767.1183</v>
+        <v>2330325.3783</v>
       </c>
       <c r="E7" s="12" t="n">
         <f aca="false">SUM('Planning financier'!N34:Q34)</f>
-        <v>351229.9072</v>
+        <v>362294.1472</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUM(B7:E7)</f>
-        <v>3946065.9763</v>
+        <v>3958688.4763</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">SUM('Planning financier'!F44:I44)</f>
-        <v>1562447.0255</v>
+        <v>1575069.5255</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">SUM('Planning financier'!J44:M44)</f>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>1562447.0255</v>
+        <v>1575069.5255</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C13" s="12" t="n">
         <f aca="false">SUM('Planning financier'!F49:I49)</f>
-        <v>1562972.0255</v>
+        <v>1575594.5255</v>
       </c>
       <c r="D13" s="12" t="n">
         <f aca="false">SUM('Planning financier'!J49:M49)</f>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">SUM(B13:E13)</f>
-        <v>3946065.9763</v>
+        <v>3958688.4763</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4015,11 +4015,11 @@
       </c>
       <c r="C18" s="12" t="n">
         <f aca="false">'Planning financier'!I53</f>
-        <v>461697.0255</v>
+        <v>474319.5255</v>
       </c>
       <c r="D18" s="12" t="n">
         <f aca="false">'Planning financier'!M53</f>
-        <v>350329.907199999</v>
+        <v>361394.1472</v>
       </c>
       <c r="E18" s="12" t="n">
         <f aca="false">'Planning financier'!Q53</f>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="F31" s="12" t="n">
         <f aca="false">F9+F10+F11</f>
-        <v>3943665.9763</v>
+        <v>3956288.4763</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4370,14 +4370,14 @@
         <v>7542</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>9338</v>
+        <v>10912</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>9825</v>
+        <v>21001</v>
       </c>
       <c r="F13" s="43" t="n">
         <f aca="false">SUM(B13:E13)</f>
-        <v>26705</v>
+        <v>39455</v>
       </c>
       <c r="G13" s="41"/>
     </row>
@@ -4395,15 +4395,15 @@
       </c>
       <c r="D14" s="43" t="n">
         <f aca="false">D7+D10+D11+D12+D13</f>
-        <v>106765</v>
+        <v>108339</v>
       </c>
       <c r="E14" s="43" t="n">
         <f aca="false">E7+E10+E11+E12+E13</f>
-        <v>108396.44</v>
+        <v>119572.44</v>
       </c>
       <c r="F14" s="43" t="n">
         <f aca="false">SUM(B14:E14)</f>
-        <v>277668.44</v>
+        <v>290418.44</v>
       </c>
       <c r="G14" s="41"/>
     </row>
@@ -4525,14 +4525,14 @@
         <v>15324.7508</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>20546.5183</v>
+        <v>22104.7783</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>21002.7292</v>
+        <v>32066.9692</v>
       </c>
       <c r="F21" s="43" t="n">
         <f aca="false">SUM(B21:E21)</f>
-        <v>56873.9983</v>
+        <v>69496.4983</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4546,14 +4546,14 @@
         <v>625.07</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>1067.65</v>
+        <v>1083.39</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>1083.9644</v>
+        <v>1195.7244</v>
       </c>
       <c r="F22" s="43" t="n">
         <f aca="false">SUM(B22:E22)</f>
-        <v>2776.6844</v>
+        <v>2904.1844</v>
       </c>
       <c r="G22" s="41"/>
     </row>
@@ -4571,15 +4571,15 @@
       </c>
       <c r="D23" s="43" t="n">
         <f aca="false">SUM(D17:D22)</f>
-        <v>106765</v>
+        <v>108339</v>
       </c>
       <c r="E23" s="43" t="n">
         <f aca="false">SUM(E17:E22)</f>
-        <v>108396.44</v>
+        <v>119572.44</v>
       </c>
       <c r="F23" s="43" t="n">
         <f aca="false">SUM(B23:E23)</f>
-        <v>277668.44</v>
+        <v>290418.44</v>
       </c>
       <c r="G23" s="41"/>
     </row>
@@ -4632,15 +4632,15 @@
       </c>
       <c r="D26" s="46" t="n">
         <f aca="false">IFERROR(D17/D14,0)</f>
-        <v>0.551727923008477</v>
+        <v>0.543712159979324</v>
       </c>
       <c r="E26" s="46" t="n">
         <f aca="false">IFERROR(E17/E14,0)</f>
-        <v>0.549571281123255</v>
+        <v>0.498204857239678</v>
       </c>
       <c r="F26" s="47" t="n">
         <f aca="false">IFERROR(F17/F14,0)</f>
-        <v>0.543896098886859</v>
+        <v>0.520017879374326</v>
       </c>
       <c r="G26" s="41"/>
     </row>
@@ -4658,15 +4658,15 @@
       </c>
       <c r="D27" s="46" t="n">
         <f aca="false">IFERROR((D18+D19+D21)/D14,0)</f>
-        <v>0.315359137357748</v>
+        <v>0.32516063744358</v>
       </c>
       <c r="E27" s="46" t="n">
         <f aca="false">IFERROR((E18+E19+E21)/E14,0)</f>
-        <v>0.317093598276844</v>
+        <v>0.379987706197181</v>
       </c>
       <c r="F27" s="47" t="n">
         <f aca="false">IFERROR((F18+F19+F21)/F14,0)</f>
-        <v>0.325465459092146</v>
+        <v>0.354639968109463</v>
       </c>
       <c r="G27" s="41"/>
     </row>

--- a/Claude outputs/Mare_Durabilis_Planning_financier_2026_2029_FDD.xlsx
+++ b/Claude outputs/Mare_Durabilis_Planning_financier_2026_2029_FDD.xlsx
@@ -459,10 +459,10 @@
     <t xml:space="preserve">Charges de personnel</t>
   </si>
   <si>
-    <t xml:space="preserve">     dont chef de projet (1 ETP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     dont protection sociale complémentaire (mutuelle Allianz, prévoyance)</t>
+    <t xml:space="preserve">     dont chef de projet — coût total employeur (salaire, cotisations, mutuelle, prévoyance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     dont protection sociale complémentaire — incluse dans la ligne précédente</t>
   </si>
   <si>
     <t xml:space="preserve">Prestations externes (juridique, ingénierie, études, communication)</t>
@@ -1746,30 +1746,30 @@
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="n">
-        <v>918.6</v>
+        <v>188.49</v>
       </c>
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="n">
-        <v>6635.8</v>
+        <v>6276.72</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="12"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12" t="n">
-        <v>6882.09</v>
+        <v>6517.17</v>
       </c>
       <c r="R17" s="12" t="n">
         <f aca="false">SUM(B17:Q17)</f>
-        <v>14436.49</v>
+        <v>12982.38</v>
       </c>
       <c r="S17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="10" t="n">
         <f aca="false">S17-R17</f>
-        <v>-14436.49</v>
+        <v>-12982.38</v>
       </c>
       <c r="U17" s="19" t="s">
         <v>41</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="T18" s="15" t="n">
         <f aca="false">T17</f>
-        <v>-14436.49</v>
+        <v>-12982.38</v>
       </c>
       <c r="U18" s="19" t="s">
         <v>43</v>
@@ -1831,55 +1831,55 @@
       </c>
       <c r="F19" s="15" t="n">
         <f aca="false">'Circuit public'!C21/4</f>
-        <v>3831.1877</v>
+        <v>2379.68395</v>
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">'Circuit public'!C21/4</f>
-        <v>3831.1877</v>
+        <v>2379.68395</v>
       </c>
       <c r="H19" s="15" t="n">
         <f aca="false">'Circuit public'!C21/4</f>
-        <v>3831.1877</v>
+        <v>2379.68395</v>
       </c>
       <c r="I19" s="15" t="n">
         <f aca="false">'Circuit public'!C21/4</f>
-        <v>3831.1877</v>
+        <v>2379.68395</v>
       </c>
       <c r="J19" s="15" t="n">
         <f aca="false">'Circuit public'!D21/4</f>
-        <v>5526.194575</v>
+        <v>4846.700825</v>
       </c>
       <c r="K19" s="15" t="n">
         <f aca="false">'Circuit public'!D21/4</f>
-        <v>5526.194575</v>
+        <v>4846.700825</v>
       </c>
       <c r="L19" s="15" t="n">
         <f aca="false">'Circuit public'!D21/4</f>
-        <v>5526.194575</v>
+        <v>4846.700825</v>
       </c>
       <c r="M19" s="15" t="n">
         <f aca="false">'Circuit public'!D21/4</f>
-        <v>5526.194575</v>
+        <v>4846.700825</v>
       </c>
       <c r="N19" s="15" t="n">
         <f aca="false">'Circuit public'!E21/4</f>
-        <v>8016.7423</v>
+        <v>7174.7776</v>
       </c>
       <c r="O19" s="15" t="n">
         <f aca="false">'Circuit public'!E21/4</f>
-        <v>8016.7423</v>
+        <v>7174.7776</v>
       </c>
       <c r="P19" s="15" t="n">
         <f aca="false">'Circuit public'!E21/4</f>
-        <v>8016.7423</v>
+        <v>7174.7776</v>
       </c>
       <c r="Q19" s="15" t="n">
         <f aca="false">'Circuit public'!E21/4</f>
-        <v>8016.7423</v>
+        <v>7174.7776</v>
       </c>
       <c r="R19" s="15" t="n">
         <f aca="false">SUM(B19:Q19)</f>
-        <v>69496.4983</v>
+        <v>57604.6495</v>
       </c>
       <c r="S19" s="15"/>
       <c r="T19" s="15"/>
@@ -1909,55 +1909,55 @@
       </c>
       <c r="F20" s="21" t="n">
         <f aca="false">SUM(F17:F19)</f>
-        <v>3831.1877</v>
+        <v>2379.68395</v>
       </c>
       <c r="G20" s="21" t="n">
         <f aca="false">SUM(G17:G19)</f>
-        <v>3831.1877</v>
+        <v>2379.68395</v>
       </c>
       <c r="H20" s="21" t="n">
         <f aca="false">SUM(H17:H19)</f>
-        <v>3831.1877</v>
+        <v>2379.68395</v>
       </c>
       <c r="I20" s="21" t="n">
         <f aca="false">SUM(I17:I19)</f>
-        <v>4749.7877</v>
+        <v>2568.17395</v>
       </c>
       <c r="J20" s="21" t="n">
         <f aca="false">SUM(J17:J19)</f>
-        <v>5526.194575</v>
+        <v>4846.700825</v>
       </c>
       <c r="K20" s="21" t="n">
         <f aca="false">SUM(K17:K19)</f>
-        <v>5526.194575</v>
+        <v>4846.700825</v>
       </c>
       <c r="L20" s="21" t="n">
         <f aca="false">SUM(L17:L19)</f>
-        <v>5526.194575</v>
+        <v>4846.700825</v>
       </c>
       <c r="M20" s="21" t="n">
         <f aca="false">SUM(M17:M19)</f>
-        <v>12161.994575</v>
+        <v>11123.420825</v>
       </c>
       <c r="N20" s="21" t="n">
         <f aca="false">SUM(N17:N19)</f>
-        <v>8016.7423</v>
+        <v>7174.7776</v>
       </c>
       <c r="O20" s="21" t="n">
         <f aca="false">SUM(O17:O19)</f>
-        <v>8016.7423</v>
+        <v>7174.7776</v>
       </c>
       <c r="P20" s="21" t="n">
         <f aca="false">SUM(P17:P19)</f>
-        <v>8016.7423</v>
+        <v>7174.7776</v>
       </c>
       <c r="Q20" s="21" t="n">
         <f aca="false">SUM(Q17:Q19)</f>
-        <v>14898.8323</v>
+        <v>13691.9476</v>
       </c>
       <c r="R20" s="15" t="n">
         <f aca="false">SUM(B20:Q20)</f>
-        <v>86052.9883</v>
+        <v>72707.0295</v>
       </c>
       <c r="S20" s="15"/>
       <c r="T20" s="15"/>
@@ -1999,47 +1999,47 @@
       <c r="G22" s="10"/>
       <c r="H22" s="11" t="n">
         <f aca="false">'Circuit public'!C18/2</f>
-        <v>2883</v>
+        <v>2842.8307</v>
       </c>
       <c r="I22" s="11" t="n">
         <f aca="false">'Circuit public'!C18/2</f>
-        <v>2883</v>
+        <v>2842.8307</v>
       </c>
       <c r="J22" s="11" t="n">
         <f aca="false">'Circuit public'!D18/4</f>
-        <v>2939.1</v>
+        <v>2899.687325</v>
       </c>
       <c r="K22" s="11" t="n">
         <f aca="false">'Circuit public'!D18/4</f>
-        <v>2939.1</v>
+        <v>2899.687325</v>
       </c>
       <c r="L22" s="11" t="n">
         <f aca="false">'Circuit public'!D18/4</f>
-        <v>2939.1</v>
+        <v>2899.687325</v>
       </c>
       <c r="M22" s="11" t="n">
         <f aca="false">'Circuit public'!D18/4</f>
-        <v>2939.1</v>
+        <v>2899.687325</v>
       </c>
       <c r="N22" s="11" t="n">
         <f aca="false">'Circuit public'!E18/4</f>
-        <v>2996.322</v>
+        <v>2957.681075</v>
       </c>
       <c r="O22" s="11" t="n">
         <f aca="false">'Circuit public'!E18/4</f>
-        <v>2996.322</v>
+        <v>2957.681075</v>
       </c>
       <c r="P22" s="11" t="n">
         <f aca="false">'Circuit public'!E18/4</f>
-        <v>2996.322</v>
+        <v>2957.681075</v>
       </c>
       <c r="Q22" s="11" t="n">
         <f aca="false">'Circuit public'!E18/4</f>
-        <v>2996.322</v>
+        <v>2957.681075</v>
       </c>
       <c r="R22" s="12" t="n">
         <f aca="false">SUM(B22:Q22)</f>
-        <v>29507.688</v>
+        <v>29115.135</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>49</v>
@@ -2309,55 +2309,55 @@
       </c>
       <c r="F28" s="22" t="n">
         <f aca="false">'Circuit public'!C19/4</f>
-        <v>309.9</v>
+        <v>147.4571</v>
       </c>
       <c r="G28" s="22" t="n">
         <f aca="false">'Circuit public'!C19/4</f>
-        <v>309.9</v>
+        <v>147.4571</v>
       </c>
       <c r="H28" s="22" t="n">
         <f aca="false">'Circuit public'!C19/4</f>
-        <v>309.9</v>
+        <v>147.4571</v>
       </c>
       <c r="I28" s="22" t="n">
         <f aca="false">'Circuit public'!C19/4</f>
-        <v>309.9</v>
+        <v>147.4571</v>
       </c>
       <c r="J28" s="22" t="n">
         <f aca="false">'Circuit public'!D19/4</f>
-        <v>341.6</v>
+        <v>291.242075</v>
       </c>
       <c r="K28" s="22" t="n">
         <f aca="false">'Circuit public'!D19/4</f>
-        <v>341.6</v>
+        <v>291.242075</v>
       </c>
       <c r="L28" s="22" t="n">
         <f aca="false">'Circuit public'!D19/4</f>
-        <v>341.6</v>
+        <v>291.242075</v>
       </c>
       <c r="M28" s="22" t="n">
         <f aca="false">'Circuit public'!D19/4</f>
-        <v>341.6</v>
+        <v>291.242075</v>
       </c>
       <c r="N28" s="22" t="n">
         <f aca="false">'Circuit public'!E19/4</f>
-        <v>345.95</v>
+        <v>293.3615</v>
       </c>
       <c r="O28" s="22" t="n">
         <f aca="false">'Circuit public'!E19/4</f>
-        <v>345.95</v>
+        <v>293.3615</v>
       </c>
       <c r="P28" s="22" t="n">
         <f aca="false">'Circuit public'!E19/4</f>
-        <v>345.95</v>
+        <v>293.3615</v>
       </c>
       <c r="Q28" s="22" t="n">
         <f aca="false">'Circuit public'!E19/4</f>
-        <v>345.95</v>
+        <v>293.3615</v>
       </c>
       <c r="R28" s="12" t="n">
         <f aca="false">SUM(B28:Q28)</f>
-        <v>3989.8</v>
+        <v>2928.2427</v>
       </c>
       <c r="U28" s="19" t="s">
         <v>61</v>
@@ -2565,55 +2565,55 @@
       </c>
       <c r="F32" s="15" t="n">
         <f aca="false">F22+F23+F24+F25+F26+F27+F28+F29+F30+F31</f>
-        <v>434.9</v>
+        <v>272.4571</v>
       </c>
       <c r="G32" s="15" t="n">
         <f aca="false">G22+G23+G24+G25+G26+G27+G28+G29+G30+G31</f>
-        <v>8434.9</v>
+        <v>8272.4571</v>
       </c>
       <c r="H32" s="15" t="n">
         <f aca="false">H22+H23+H24+H25+H26+H27+H28+H29+H30+H31</f>
-        <v>15592.9</v>
+        <v>15390.2878</v>
       </c>
       <c r="I32" s="15" t="n">
         <f aca="false">I22+I23+I24+I25+I26+I27+I28+I29+I30+I31</f>
-        <v>8592.9</v>
+        <v>8390.2878</v>
       </c>
       <c r="J32" s="15" t="n">
         <f aca="false">J22+J23+J24+J25+J26+J27+J28+J29+J30+J31</f>
-        <v>23308.7</v>
+        <v>23218.9294</v>
       </c>
       <c r="K32" s="15" t="n">
         <f aca="false">K22+K23+K24+K25+K26+K27+K28+K29+K30+K31</f>
-        <v>16308.7</v>
+        <v>16218.9294</v>
       </c>
       <c r="L32" s="15" t="n">
         <f aca="false">L22+L23+L24+L25+L26+L27+L28+L29+L30+L31</f>
-        <v>8308.7</v>
+        <v>8218.9294</v>
       </c>
       <c r="M32" s="15" t="n">
         <f aca="false">M22+M23+M24+M25+M26+M27+M28+M29+M30+M31</f>
-        <v>12308.7</v>
+        <v>12218.9294</v>
       </c>
       <c r="N32" s="15" t="n">
         <f aca="false">N22+N23+N24+N25+N26+N27+N28+N29+N30+N31</f>
-        <v>23373.772</v>
+        <v>23282.542575</v>
       </c>
       <c r="O32" s="15" t="n">
         <f aca="false">O22+O23+O24+O25+O26+O27+O28+O29+O30+O31</f>
-        <v>16373.772</v>
+        <v>16282.542575</v>
       </c>
       <c r="P32" s="15" t="n">
         <f aca="false">P22+P23+P24+P25+P26+P27+P28+P29+P30+P31</f>
-        <v>8373.772</v>
+        <v>8282.542575</v>
       </c>
       <c r="Q32" s="15" t="n">
         <f aca="false">Q22+Q23+Q24+Q25+Q26+Q27+Q28+Q29+Q30+Q31</f>
-        <v>14373.772</v>
+        <v>14282.542575</v>
       </c>
       <c r="R32" s="15" t="n">
         <f aca="false">SUM(B32:Q32)</f>
-        <v>156085.488</v>
+        <v>154631.3777</v>
       </c>
       <c r="U32" s="13" t="s">
         <v>69</v>
@@ -2642,55 +2642,55 @@
       </c>
       <c r="F34" s="23" t="n">
         <f aca="false">F13+F20+F32</f>
-        <v>112616.0877</v>
+        <v>111002.14105</v>
       </c>
       <c r="G34" s="23" t="n">
         <f aca="false">G13+G20+G32</f>
-        <v>162266.0877</v>
+        <v>160652.14105</v>
       </c>
       <c r="H34" s="23" t="n">
         <f aca="false">H13+H20+H32</f>
-        <v>819424.0877</v>
+        <v>817769.97175</v>
       </c>
       <c r="I34" s="23" t="n">
         <f aca="false">I13+I20+I32</f>
-        <v>56342.6877</v>
+        <v>53958.46175</v>
       </c>
       <c r="J34" s="23" t="n">
         <f aca="false">J13+J20+J32</f>
-        <v>77184.894575</v>
+        <v>76415.630225</v>
       </c>
       <c r="K34" s="23" t="n">
         <f aca="false">K13+K20+K32</f>
-        <v>171834.894575</v>
+        <v>171065.630225</v>
       </c>
       <c r="L34" s="23" t="n">
         <f aca="false">L13+L20+L32</f>
-        <v>2013834.894575</v>
+        <v>2013065.630225</v>
       </c>
       <c r="M34" s="23" t="n">
         <f aca="false">M13+M20+M32</f>
-        <v>67470.694575</v>
+        <v>66342.350225</v>
       </c>
       <c r="N34" s="23" t="n">
         <f aca="false">N13+N20+N32</f>
-        <v>99240.5143</v>
+        <v>98307.320175</v>
       </c>
       <c r="O34" s="23" t="n">
         <f aca="false">O13+O20+O32</f>
-        <v>174390.5143</v>
+        <v>173457.320175</v>
       </c>
       <c r="P34" s="23" t="n">
         <f aca="false">P13+P20+P32</f>
-        <v>16390.5143</v>
+        <v>15457.320175</v>
       </c>
       <c r="Q34" s="23" t="n">
         <f aca="false">Q13+Q20+Q32</f>
-        <v>72272.6043</v>
+        <v>70974.490175</v>
       </c>
       <c r="R34" s="23" t="n">
         <f aca="false">SUM(B34:Q34)</f>
-        <v>3958688.4763</v>
+        <v>3943888.4072</v>
       </c>
       <c r="S34" s="8"/>
       <c r="T34" s="8"/>
@@ -2718,51 +2718,51 @@
       </c>
       <c r="F35" s="15" t="n">
         <f aca="false">E35+F34</f>
-        <v>228036.0877</v>
+        <v>226422.14105</v>
       </c>
       <c r="G35" s="15" t="n">
         <f aca="false">F35+G34</f>
-        <v>390302.1754</v>
+        <v>387074.2821</v>
       </c>
       <c r="H35" s="15" t="n">
         <f aca="false">G35+H34</f>
-        <v>1209726.2631</v>
+        <v>1204844.25385</v>
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">H35+I34</f>
-        <v>1266068.9508</v>
+        <v>1258802.7156</v>
       </c>
       <c r="J35" s="15" t="n">
         <f aca="false">I35+J34</f>
-        <v>1343253.845375</v>
+        <v>1335218.345825</v>
       </c>
       <c r="K35" s="15" t="n">
         <f aca="false">J35+K34</f>
-        <v>1515088.73995</v>
+        <v>1506283.97605</v>
       </c>
       <c r="L35" s="15" t="n">
         <f aca="false">K35+L34</f>
-        <v>3528923.634525</v>
+        <v>3519349.606275</v>
       </c>
       <c r="M35" s="15" t="n">
         <f aca="false">L35+M34</f>
-        <v>3596394.3291</v>
+        <v>3585691.9565</v>
       </c>
       <c r="N35" s="15" t="n">
         <f aca="false">M35+N34</f>
-        <v>3695634.8434</v>
+        <v>3683999.276675</v>
       </c>
       <c r="O35" s="15" t="n">
         <f aca="false">N35+O34</f>
-        <v>3870025.3577</v>
+        <v>3857456.59685</v>
       </c>
       <c r="P35" s="15" t="n">
         <f aca="false">O35+P34</f>
-        <v>3886415.872</v>
+        <v>3872913.917025</v>
       </c>
       <c r="Q35" s="15" t="n">
         <f aca="false">P35+Q34</f>
-        <v>3958688.4763</v>
+        <v>3943888.4072</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3009,7 +3009,7 @@
       <c r="D43" s="27"/>
       <c r="E43" s="28" t="n">
         <f aca="false">E9+E10+SUM(B20:I20)+SUM(B32:I32)</f>
-        <v>164718.9508</v>
+        <v>157452.7156</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="27"/>
@@ -3025,7 +3025,7 @@
       <c r="Q43" s="27"/>
       <c r="R43" s="12" t="n">
         <f aca="false">SUM(B43:Q43)</f>
-        <v>164718.9508</v>
+        <v>157452.7156</v>
       </c>
       <c r="U43" s="13" t="s">
         <v>81</v>
@@ -3040,7 +3040,7 @@
       <c r="E44" s="29"/>
       <c r="F44" s="28" t="n">
         <f aca="false">MAX(0,K35-SUM(B40:K40)-R43)+SUM(L20:Q20)+SUM(L32:Q32)+M9+Q9</f>
-        <v>1575069.5255</v>
+        <v>1567535.6916</v>
       </c>
       <c r="G44" s="27"/>
       <c r="H44" s="27"/>
@@ -3055,7 +3055,7 @@
       <c r="Q44" s="27"/>
       <c r="R44" s="12" t="n">
         <f aca="false">SUM(B44:Q44)</f>
-        <v>1575069.5255</v>
+        <v>1567535.6916</v>
       </c>
       <c r="U44" s="13" t="s">
         <v>83</v>
@@ -3306,11 +3306,11 @@
       </c>
       <c r="E49" s="23" t="n">
         <f aca="false">SUM(E43:E48)</f>
-        <v>164793.9508</v>
+        <v>157527.7156</v>
       </c>
       <c r="F49" s="23" t="n">
         <f aca="false">SUM(F43:F48)</f>
-        <v>1575144.5255</v>
+        <v>1567610.6916</v>
       </c>
       <c r="G49" s="23" t="n">
         <f aca="false">SUM(G43:G48)</f>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="R49" s="23" t="n">
         <f aca="false">SUM(B49:Q49)</f>
-        <v>3958688.4763</v>
+        <v>3943888.4072</v>
       </c>
       <c r="S49" s="8"/>
       <c r="T49" s="8"/>
@@ -3382,55 +3382,55 @@
       </c>
       <c r="E50" s="15" t="n">
         <f aca="false">D50+E49</f>
-        <v>164793.9508</v>
+        <v>157527.7156</v>
       </c>
       <c r="F50" s="15" t="n">
         <f aca="false">E50+F49</f>
-        <v>1739938.4763</v>
+        <v>1725138.4072</v>
       </c>
       <c r="G50" s="15" t="n">
         <f aca="false">F50+G49</f>
-        <v>1740088.4763</v>
+        <v>1725288.4072</v>
       </c>
       <c r="H50" s="15" t="n">
         <f aca="false">G50+H49</f>
-        <v>1740238.4763</v>
+        <v>1725438.4072</v>
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">H50+I49</f>
-        <v>1740388.4763</v>
+        <v>1725588.4072</v>
       </c>
       <c r="J50" s="15" t="n">
         <f aca="false">I50+J49</f>
-        <v>1740613.4763</v>
+        <v>1725813.4072</v>
       </c>
       <c r="K50" s="15" t="n">
         <f aca="false">J50+K49</f>
-        <v>3957338.4763</v>
+        <v>3942538.4072</v>
       </c>
       <c r="L50" s="15" t="n">
         <f aca="false">K50+L49</f>
-        <v>3957563.4763</v>
+        <v>3942763.4072</v>
       </c>
       <c r="M50" s="15" t="n">
         <f aca="false">L50+M49</f>
-        <v>3957788.4763</v>
+        <v>3942988.4072</v>
       </c>
       <c r="N50" s="15" t="n">
         <f aca="false">M50+N49</f>
-        <v>3958013.4763</v>
+        <v>3943213.4072</v>
       </c>
       <c r="O50" s="15" t="n">
         <f aca="false">N50+O49</f>
-        <v>3958238.4763</v>
+        <v>3943438.4072</v>
       </c>
       <c r="P50" s="15" t="n">
         <f aca="false">O50+P49</f>
-        <v>3958463.4763</v>
+        <v>3943663.4072</v>
       </c>
       <c r="Q50" s="15" t="n">
         <f aca="false">P50+Q49</f>
-        <v>3958688.4763</v>
+        <v>3943888.4072</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3477,51 +3477,51 @@
       </c>
       <c r="E53" s="10" t="n">
         <f aca="false">E50-E35</f>
-        <v>49373.9508</v>
+        <v>42107.7156</v>
       </c>
       <c r="F53" s="10" t="n">
         <f aca="false">F50-F35</f>
-        <v>1511902.3886</v>
+        <v>1498716.26615</v>
       </c>
       <c r="G53" s="10" t="n">
         <f aca="false">G50-G35</f>
-        <v>1349786.3009</v>
+        <v>1338214.1251</v>
       </c>
       <c r="H53" s="10" t="n">
         <f aca="false">H50-H35</f>
-        <v>530512.2132</v>
+        <v>520594.15335</v>
       </c>
       <c r="I53" s="10" t="n">
         <f aca="false">I50-I35</f>
-        <v>474319.5255</v>
+        <v>466785.6916</v>
       </c>
       <c r="J53" s="10" t="n">
         <f aca="false">J50-J35</f>
-        <v>397359.630925</v>
+        <v>390595.061375</v>
       </c>
       <c r="K53" s="10" t="n">
         <f aca="false">K50-K35</f>
-        <v>2442249.73635</v>
+        <v>2436254.43115</v>
       </c>
       <c r="L53" s="10" t="n">
         <f aca="false">L50-L35</f>
-        <v>428639.841775</v>
+        <v>423413.800925</v>
       </c>
       <c r="M53" s="10" t="n">
         <f aca="false">M50-M35</f>
-        <v>361394.1472</v>
+        <v>357296.4507</v>
       </c>
       <c r="N53" s="10" t="n">
         <f aca="false">N50-N35</f>
-        <v>262378.6329</v>
+        <v>259214.130525</v>
       </c>
       <c r="O53" s="10" t="n">
         <f aca="false">O50-O35</f>
-        <v>88213.1186000002</v>
+        <v>85981.8103499999</v>
       </c>
       <c r="P53" s="10" t="n">
         <f aca="false">P50-P35</f>
-        <v>72047.6043000002</v>
+        <v>70749.4901749999</v>
       </c>
       <c r="Q53" s="10" t="n">
         <f aca="false">Q50-Q35</f>
@@ -3763,19 +3763,19 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">SUM('Planning financier'!F20:I20)</f>
-        <v>16243.3508</v>
+        <v>9707.2258</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">SUM('Planning financier'!J20:M20)</f>
-        <v>28740.5783</v>
+        <v>25663.5233</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">SUM('Planning financier'!N20:Q20)</f>
-        <v>38949.0592</v>
+        <v>35216.2804</v>
       </c>
       <c r="F5" s="12" t="n">
         <f aca="false">SUM(B5:E5)</f>
-        <v>86052.9883</v>
+        <v>72707.0295</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3788,19 +3788,19 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">SUM('Planning financier'!F32:I32)</f>
-        <v>33055.6</v>
+        <v>32325.4898</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">SUM('Planning financier'!J32:M32)</f>
-        <v>60234.8</v>
+        <v>59875.7176</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">SUM('Planning financier'!N32:Q32)</f>
-        <v>62495.088</v>
+        <v>62130.1703</v>
       </c>
       <c r="F6" s="12" t="n">
         <f aca="false">SUM(B6:E6)</f>
-        <v>156085.488</v>
+        <v>154631.3777</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3813,19 +3813,19 @@
       </c>
       <c r="C7" s="12" t="n">
         <f aca="false">SUM('Planning financier'!F34:I34)</f>
-        <v>1150648.9508</v>
+        <v>1143382.7156</v>
       </c>
       <c r="D7" s="12" t="n">
         <f aca="false">SUM('Planning financier'!J34:M34)</f>
-        <v>2330325.3783</v>
+        <v>2326889.2409</v>
       </c>
       <c r="E7" s="12" t="n">
         <f aca="false">SUM('Planning financier'!N34:Q34)</f>
-        <v>362294.1472</v>
+        <v>358196.4507</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUM(B7:E7)</f>
-        <v>3958688.4763</v>
+        <v>3943888.4072</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">SUM('Planning financier'!B43:E43)</f>
-        <v>164718.9508</v>
+        <v>157452.7156</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">SUM('Planning financier'!F43:I43)</f>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">SUM(B9:E9)</f>
-        <v>164718.9508</v>
+        <v>157452.7156</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">SUM('Planning financier'!F44:I44)</f>
-        <v>1575069.5255</v>
+        <v>1567535.6916</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">SUM('Planning financier'!J44:M44)</f>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>1575069.5255</v>
+        <v>1567535.6916</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3934,11 +3934,11 @@
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">SUM('Planning financier'!B49:E49)</f>
-        <v>164793.9508</v>
+        <v>157527.7156</v>
       </c>
       <c r="C13" s="12" t="n">
         <f aca="false">SUM('Planning financier'!F49:I49)</f>
-        <v>1575594.5255</v>
+        <v>1568060.6916</v>
       </c>
       <c r="D13" s="12" t="n">
         <f aca="false">SUM('Planning financier'!J49:M49)</f>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">SUM(B13:E13)</f>
-        <v>3958688.4763</v>
+        <v>3943888.4072</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4011,15 +4011,15 @@
       </c>
       <c r="B18" s="12" t="n">
         <f aca="false">'Planning financier'!E53</f>
-        <v>49373.9508</v>
+        <v>42107.7156</v>
       </c>
       <c r="C18" s="12" t="n">
         <f aca="false">'Planning financier'!I53</f>
-        <v>474319.5255</v>
+        <v>466785.6916</v>
       </c>
       <c r="D18" s="12" t="n">
         <f aca="false">'Planning financier'!M53</f>
-        <v>361394.1472</v>
+        <v>357296.4507</v>
       </c>
       <c r="E18" s="12" t="n">
         <f aca="false">'Planning financier'!Q53</f>
@@ -4040,17 +4040,17 @@
         <v>300</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>33055.6</v>
+        <v>32325.49</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>60234.8</v>
+        <v>59875.72</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>62495.09</v>
+        <v>62130.17</v>
       </c>
       <c r="F21" s="12" t="n">
         <f aca="false">SUM(B21:E21)</f>
-        <v>156085.49</v>
+        <v>154631.38</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4063,19 +4063,19 @@
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">C21-C6</f>
-        <v>0</v>
+        <v>0.000199999998585554</v>
       </c>
       <c r="D22" s="12" t="n">
         <f aca="false">D21-D6</f>
-        <v>0</v>
+        <v>0.00240000000485452</v>
       </c>
       <c r="E22" s="12" t="n">
         <f aca="false">E21-E6</f>
-        <v>0.0019999999931315</v>
+        <v>-0.00029999999969732</v>
       </c>
       <c r="F22" s="12" t="n">
         <f aca="false">F21-F6</f>
-        <v>0.00199999997857958</v>
+        <v>0.00229999999282882</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="F31" s="12" t="n">
         <f aca="false">F9+F10+F11</f>
-        <v>3956288.4763</v>
+        <v>3941488.4072</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4235,17 +4235,17 @@
         <v>0</v>
       </c>
       <c r="C7" s="42" t="n">
-        <v>28830</v>
+        <v>28428.3072</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>58782</v>
+        <v>57993.7467</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>59926.44</v>
+        <v>59153.6216</v>
       </c>
       <c r="F7" s="43" t="n">
         <f aca="false">SUM(B7:E7)</f>
-        <v>147538.44</v>
+        <v>145575.6755</v>
       </c>
       <c r="G7" s="41"/>
     </row>
@@ -4257,17 +4257,17 @@
         <v>0</v>
       </c>
       <c r="C8" s="42" t="n">
-        <v>28050</v>
+        <v>28428.3072</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>57222</v>
+        <v>57993.7467</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>58366.44</v>
+        <v>59153.6216</v>
       </c>
       <c r="F8" s="43" t="n">
         <f aca="false">SUM(B8:E8)</f>
-        <v>143638.44</v>
+        <v>145575.6755</v>
       </c>
       <c r="G8" s="41"/>
     </row>
@@ -4279,17 +4279,17 @@
         <v>0</v>
       </c>
       <c r="C9" s="42" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>1560</v>
+        <v>0</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>1560</v>
+        <v>0</v>
       </c>
       <c r="F9" s="43" t="n">
         <f aca="false">SUM(B9:E9)</f>
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="G9" s="41"/>
     </row>
@@ -4301,17 +4301,17 @@
         <v>0</v>
       </c>
       <c r="C10" s="42" t="n">
-        <v>17345</v>
+        <v>16123.8</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>26915</v>
+        <v>25866.904</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>26915</v>
+        <v>25883.9421</v>
       </c>
       <c r="F10" s="43" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>71175</v>
+        <v>67874.6461</v>
       </c>
       <c r="G10" s="41"/>
     </row>
@@ -4323,17 +4323,17 @@
         <v>0</v>
       </c>
       <c r="C11" s="42" t="n">
-        <v>7590</v>
+        <v>3544</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>10680</v>
+        <v>7088</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>10680</v>
+        <v>7088</v>
       </c>
       <c r="F11" s="43" t="n">
         <f aca="false">SUM(B11:E11)</f>
-        <v>28950</v>
+        <v>17720</v>
       </c>
       <c r="G11" s="41"/>
     </row>
@@ -4345,17 +4345,17 @@
         <v>0</v>
       </c>
       <c r="C12" s="42" t="n">
-        <v>1200</v>
+        <v>286.76</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>1050</v>
+        <v>528.92</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>1050</v>
+        <v>534.428</v>
       </c>
       <c r="F12" s="43" t="n">
         <f aca="false">SUM(B12:E12)</f>
-        <v>3300</v>
+        <v>1350.108</v>
       </c>
       <c r="G12" s="41"/>
     </row>
@@ -4367,17 +4367,17 @@
         <v>0</v>
       </c>
       <c r="C13" s="42" t="n">
-        <v>7542</v>
+        <v>3815.942</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>10912</v>
+        <v>9557.9614</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>21001</v>
+        <v>18968.0404</v>
       </c>
       <c r="F13" s="43" t="n">
         <f aca="false">SUM(B13:E13)</f>
-        <v>39455</v>
+        <v>32341.9438</v>
       </c>
       <c r="G13" s="41"/>
     </row>
@@ -4391,19 +4391,19 @@
       </c>
       <c r="C14" s="43" t="n">
         <f aca="false">C7+C10+C11+C12+C13</f>
-        <v>62507</v>
+        <v>52198.8092</v>
       </c>
       <c r="D14" s="43" t="n">
         <f aca="false">D7+D10+D11+D12+D13</f>
-        <v>108339</v>
+        <v>101035.5321</v>
       </c>
       <c r="E14" s="43" t="n">
         <f aca="false">E7+E10+E11+E12+E13</f>
-        <v>119572.44</v>
+        <v>111628.0321</v>
       </c>
       <c r="F14" s="43" t="n">
         <f aca="false">SUM(B14:E14)</f>
-        <v>290418.44</v>
+        <v>264862.3734</v>
       </c>
       <c r="G14" s="41"/>
     </row>
@@ -4435,17 +4435,17 @@
         <v>0</v>
       </c>
       <c r="C17" s="42" t="n">
-        <v>32545.9792</v>
+        <v>29607.1056</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>58905.2317</v>
+        <v>55110.9383</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>59571.5704</v>
+        <v>55804.3007</v>
       </c>
       <c r="F17" s="43" t="n">
         <f aca="false">SUM(B17:E17)</f>
-        <v>151022.7813</v>
+        <v>140522.3446</v>
       </c>
       <c r="G17" s="41"/>
     </row>
@@ -4457,17 +4457,17 @@
         <v>0</v>
       </c>
       <c r="C18" s="42" t="n">
-        <v>5766</v>
+        <v>5685.6614</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>11756.4</v>
+        <v>11598.7493</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>11985.288</v>
+        <v>11830.7243</v>
       </c>
       <c r="F18" s="43" t="n">
         <f aca="false">SUM(B18:E18)</f>
-        <v>29507.688</v>
+        <v>29115.135</v>
       </c>
       <c r="G18" s="41"/>
     </row>
@@ -4479,17 +4479,17 @@
         <v>0</v>
       </c>
       <c r="C19" s="42" t="n">
-        <v>1239.6</v>
+        <v>589.8284</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>1366.4</v>
+        <v>1164.9683</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>1383.8</v>
+        <v>1173.446</v>
       </c>
       <c r="F19" s="43" t="n">
         <f aca="false">SUM(B19:E19)</f>
-        <v>3989.8</v>
+        <v>2928.2427</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4500,17 +4500,17 @@
         <v>0</v>
       </c>
       <c r="C20" s="42" t="n">
-        <v>7005.6</v>
+        <v>6275.4898</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>13122.8</v>
+        <v>12763.7176</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>13369.088</v>
+        <v>13004.1703</v>
       </c>
       <c r="F20" s="43" t="n">
         <f aca="false">SUM(B20:E20)</f>
-        <v>33497.488</v>
+        <v>32043.3777</v>
       </c>
       <c r="G20" s="41"/>
     </row>
@@ -4522,17 +4522,17 @@
         <v>0</v>
       </c>
       <c r="C21" s="42" t="n">
-        <v>15324.7508</v>
+        <v>9518.7358</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>22104.7783</v>
+        <v>19386.8033</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>32066.9692</v>
+        <v>28699.1104</v>
       </c>
       <c r="F21" s="43" t="n">
         <f aca="false">SUM(B21:E21)</f>
-        <v>69496.4983</v>
+        <v>57604.6495</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4543,17 +4543,17 @@
         <v>0</v>
       </c>
       <c r="C22" s="42" t="n">
-        <v>625.07</v>
+        <v>521.9881</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>1083.39</v>
+        <v>1010.3553</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>1195.7244</v>
+        <v>1116.2803</v>
       </c>
       <c r="F22" s="43" t="n">
         <f aca="false">SUM(B22:E22)</f>
-        <v>2904.1844</v>
+        <v>2648.6237</v>
       </c>
       <c r="G22" s="41"/>
     </row>
@@ -4567,19 +4567,19 @@
       </c>
       <c r="C23" s="43" t="n">
         <f aca="false">SUM(C17:C22)</f>
-        <v>62507</v>
+        <v>52198.8091</v>
       </c>
       <c r="D23" s="43" t="n">
         <f aca="false">SUM(D17:D22)</f>
-        <v>108339</v>
+        <v>101035.5321</v>
       </c>
       <c r="E23" s="43" t="n">
         <f aca="false">SUM(E17:E22)</f>
-        <v>119572.44</v>
+        <v>111628.032</v>
       </c>
       <c r="F23" s="43" t="n">
         <f aca="false">SUM(B23:E23)</f>
-        <v>290418.44</v>
+        <v>264862.3732</v>
       </c>
       <c r="G23" s="41"/>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C24" s="45" t="n">
         <f aca="false">C23-C14</f>
-        <v>0</v>
+        <v>-0.000100000004749745</v>
       </c>
       <c r="D24" s="45" t="n">
         <f aca="false">D23-D14</f>
@@ -4601,11 +4601,11 @@
       </c>
       <c r="E24" s="45" t="n">
         <f aca="false">E23-E14</f>
-        <v>0</v>
+        <v>-9.99999901978299E-005</v>
       </c>
       <c r="F24" s="43" t="n">
         <f aca="false">SUM(B24:E24)</f>
-        <v>0</v>
+        <v>-0.000199999994947575</v>
       </c>
       <c r="G24" s="41"/>
     </row>
@@ -4628,19 +4628,19 @@
       </c>
       <c r="C26" s="46" t="n">
         <f aca="false">IFERROR(C17/C14,0)</f>
-        <v>0.52067735133665</v>
+        <v>0.567198870122884</v>
       </c>
       <c r="D26" s="46" t="n">
         <f aca="false">IFERROR(D17/D14,0)</f>
-        <v>0.543712159979324</v>
+        <v>0.545460959669653</v>
       </c>
       <c r="E26" s="46" t="n">
         <f aca="false">IFERROR(E17/E14,0)</f>
-        <v>0.498204857239678</v>
+        <v>0.499912966753805</v>
       </c>
       <c r="F26" s="47" t="n">
         <f aca="false">IFERROR(F17/F14,0)</f>
-        <v>0.520017879374326</v>
+        <v>0.530548536570654</v>
       </c>
       <c r="G26" s="41"/>
     </row>
@@ -4654,19 +4654,19 @@
       </c>
       <c r="C27" s="46" t="n">
         <f aca="false">IFERROR((C18+C19+C21)/C14,0)</f>
-        <v>0.357245601292655</v>
+        <v>0.302578274141932</v>
       </c>
       <c r="D27" s="46" t="n">
         <f aca="false">IFERROR((D18+D19+D21)/D14,0)</f>
-        <v>0.32516063744358</v>
+        <v>0.318210041871002</v>
       </c>
       <c r="E27" s="46" t="n">
         <f aca="false">IFERROR((E18+E19+E21)/E14,0)</f>
-        <v>0.379987706197181</v>
+        <v>0.373591470847044</v>
       </c>
       <c r="F27" s="47" t="n">
         <f aca="false">IFERROR((F18+F19+F21)/F14,0)</f>
-        <v>0.354639968109463</v>
+        <v>0.338470225306831</v>
       </c>
       <c r="G27" s="41"/>
     </row>
